--- a/data/3.Model_Outputs.xlsx
+++ b/data/3.Model_Outputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aheller\Documents\GitHub\TEACART\TEACART\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDA2305-2476-411F-A178-F630395CF645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{AFDA2305-2476-411F-A178-F630395CF645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8984978A-9028-4D55-B3F0-537BAE83C775}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10380" activeTab="1" xr2:uid="{4F5F78F3-96D9-4679-993C-1A62D8B147AF}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{4F5F78F3-96D9-4679-993C-1A62D8B147AF}"/>
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="2" r:id="rId1"/>
@@ -192,9 +192,6 @@
     <t>Arterial</t>
   </si>
   <si>
-    <t>Medium and Heavy Duty Vehicle Replacement (Electrification)</t>
-  </si>
-  <si>
     <t>Light Truck</t>
   </si>
   <si>
@@ -252,12 +249,6 @@
     <t>Emissions (MT CO2e)</t>
   </si>
   <si>
-    <t>Light Duty Vehicles</t>
-  </si>
-  <si>
-    <t>Medium and Heavy Duty Trucks</t>
-  </si>
-  <si>
     <t>Public Transit</t>
   </si>
   <si>
@@ -283,6 +274,15 @@
   </si>
   <si>
     <t>EVSI Type</t>
+  </si>
+  <si>
+    <t>Medium- and Heavy-Duty Vehicle Replacement (Electrification)</t>
+  </si>
+  <si>
+    <t>Medium- and Heavy-Duty Trucks</t>
+  </si>
+  <si>
+    <t>Light-Duty Vehicles</t>
   </si>
 </sst>
 </file>
@@ -371,9 +371,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -411,7 +411,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -517,7 +517,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -659,7 +659,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -668,9 +668,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F71ACC-058A-4C63-A9D5-036EACC3ACE1}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="21.31640625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="21.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -678,15 +678,15 @@
         <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -698,9 +698,9 @@
         <v>16926660.57603753</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -712,9 +712,9 @@
         <v>17657201.719608374</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -726,9 +726,9 @@
         <v>17122996.212806035</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -740,9 +740,9 @@
         <v>16561170.578931591</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -754,9 +754,9 @@
         <v>5594752.0342581868</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -768,9 +768,9 @@
         <v>5580876.1900547715</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -782,9 +782,9 @@
         <v>5264095.3981179688</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -796,9 +796,9 @@
         <v>5261934.5163450828</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -810,9 +810,9 @@
         <v>12937</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -824,9 +824,9 @@
         <v>13314</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -838,9 +838,9 @@
         <v>13471</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -852,9 +852,9 @@
         <v>10984</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -866,9 +866,9 @@
         <v>76608.001955410014</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -880,9 +880,9 @@
         <v>76608.001955410014</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -894,9 +894,9 @@
         <v>76608.001955410014</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -908,9 +908,9 @@
         <v>76608.001955410014</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -922,9 +922,9 @@
         <v>56162.315418065504</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -936,9 +936,9 @@
         <v>57720.243473599039</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -950,9 +950,9 @@
         <v>59728.566536680904</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -964,9 +964,9 @@
         <v>68485.375676508644</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -978,9 +978,9 @@
         <v>33807</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -992,9 +992,9 @@
         <v>156730</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1006,9 +1006,9 @@
         <v>34757</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1020,9 +1020,9 @@
         <v>57171</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1034,9 +1034,9 @@
         <v>22521412.610295717</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1048,9 +1048,9 @@
         <v>23238077.909663144</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1062,9 +1062,9 @@
         <v>22387091.610924006</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1076,9 +1076,9 @@
         <v>21823105.095276672</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1090,9 +1090,9 @@
         <v>45222339.53796491</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1104,9 +1104,9 @@
         <v>44958747.790340096</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1118,9 +1118,9 @@
         <v>73518018.499892294</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1132,9 +1132,9 @@
         <v>101353770.07742636</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -1146,9 +1146,9 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1160,9 +1160,9 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1174,9 +1174,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1199,14 +1199,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9482246E-1CDD-49BA-9361-347CF816C932}">
   <dimension ref="A1:K340"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.04296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.6328125" bestFit="1" customWidth="1"/>
@@ -1224,7 +1224,7 @@
     <col min="43" max="43" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
         <v>23</v>
@@ -1259,7 +1259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>-1227.9513483440437</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>-674.3594178457821</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>-159.95142184763185</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>-39.363277578159305</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>-5053.9706756788928</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>-3380.0100180201689</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>-1069.6234234241044</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>-267.40585585602611</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>-1506.5886584198779</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>-1007.5809863718124</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>-318.85474252272547</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>-79.713685630681383</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>-665.93731587650711</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>-258.47226886060952</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>-13.776003670119099</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>-2.6492314750229031</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>-404.4641459579542</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>-212.1096759869786</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>-420.22869002246358</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>-250.49259578839377</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>-62.623148947098443</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>-3942673.2340116268</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>-2165215.1206395347</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>-513567.73255813948</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>-126386.55523255812</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>-16227153.409090908</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>-10852445.454545451</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>-3434318.1818181821</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>-858579.54545454553</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>-4837314.4312499994</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>-3235113.9899999993</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>-1023770.2499999999</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>-255942.56250000003</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>-2138173.6616654824</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>-829895.82408558216</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>-44231.622869318184</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>-8506.0813210227261</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>-1298642.6249999998</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>-681036.05514705868</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>-1349258.9999999995</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>-804274.90394048393</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>-201068.72598512098</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>-3.9426732340116266</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>-2.1652151206395347</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>-0.51356773255813948</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>-0.12638655523255812</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>-16.227153409090906</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>-10.852445454545451</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>-3.434318181818182</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>-0.85857954545454551</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>-4.8373144312499994</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>-3.235113989999999</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>-1.0237702499999999</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>-0.25594256250000003</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>-2.1381736616654825</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>-0.82989582408558216</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>-4.4231622869318185E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>-8.5060813210227262E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>-1.2986426249999996</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>-0.68103605514705867</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>-1.3492589999999995</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>-0.80427490394048395</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>-0.20106872598512099</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>-3.4886035989717228E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>-1.9158517112830554E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>-4.5442118425196108E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>-1.1183087343947017E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>-0.14358305247229594</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>-9.6025914457662453E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>-3.0387947613184325E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>-7.5969869032960812E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>-4.2802107941991414E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>-2.8625325099829173E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>-9.0586471834902451E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>-2.2646617958725617E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>-1.8919245619863492E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>-7.3431841464851877E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>-3.9137557076536657E-4</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>-7.5264532839493546E-5</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>-1.1490806025391565E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>-6.0260252169011671E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>-1.1938675928655735E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>17</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>-7.1164820362111065E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>-1.7791205090527766E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>19622.093023255813</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>7350</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>1177.3255813953488</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>40909.090909090912</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>21818.18181818182</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>6818.181818181818</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>1363.6363636363637</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>12195</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>6504</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>2032.5</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>406.5</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>17711.292613636364</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>5482.0667613636369</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>288.52982954545456</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>44.389204545454547</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>7900</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>2885.294117647059</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>8230</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>1596.7339764551994</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>319.34679529103988</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>21</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>46.026241583586391</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>21</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>56.401517470719497</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>21</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>36.315541363186675</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>21</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>47.183012855841476</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>21</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>-117.66811971865421</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>21</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>-58.765712240573713</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>21</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>-322195.23325198208</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>21</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>-246095.1251973084</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>21</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>-323051.61352126248</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>21</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>-244517.72410867043</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>21</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>-501267.70740423072</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>-266918.65952753823</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>21</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>0.57952799864563909</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>21</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>0.53719654750813439</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>21</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>0.26553834592667153</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>21</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>0.24954347422019504</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>-0.14794738136568972</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>21</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>-8.2438661521095372E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>21</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>1.0889544678880462E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>21</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>1.0311947000618089E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>21</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>1.6360856938569759E-4</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>21</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>5.5852384824023836E-4</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>21</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>-3.9828364066055383E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>21</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>-2.0750162854101589E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>21</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>601.4130598022</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>21</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>376.5457965878947</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>21</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>603.01158834932892</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>21</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>374.13224309314921</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>21</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>935.67165053071972</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>21</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>408.40751800909379</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>28</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>201.2495282251644</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>28</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>159.56040668042198</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>28</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>210.00753749789411</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>28</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>161.11290497719233</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>28</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>46.25479655211452</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>28</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>3.2585035165094305</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>28</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>111616.55672394219</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>28</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>8837.9984520664493</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>28</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>110564.59044065086</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>28</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>8391.2150289913843</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>28</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>149076.76070336619</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>28</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>10954.505887140313</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>28</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>0.35877038226534602</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>28</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>0.31643897089792766</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>28</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>0.78382625478469858</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>28</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>0.68721825231859424</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>28</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>-3.740389416065304E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>28</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>-5.9310819810709133E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>28</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>1.0985512614203797E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>28</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>9.4948732848235788E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>28</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>7.7744078971895897E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>6.2094941890566673E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>28</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>2.2033970852363164E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>28</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>8.6988539656273082E-4</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>28</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>73.655318048838552</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>28</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>98.584872471446161</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>28</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>72.961129718301592</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>28</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>93.601155057927855</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>28</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>98.375156388798686</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>28</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>122.19379441268477</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>32</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>-9.9309563361854511</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>32</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>-31886.048081317265</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>32</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>-7.111211285235116E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>32</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>-2.8213796957321161E-4</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>32</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>44.973819334335879</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>34</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>34</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>34</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>34</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>34</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>34</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>34</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>34</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>34</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>34</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>34</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>34</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>34</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>34</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>34</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>34</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>34</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>34</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>34</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>34</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>34</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>34</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>34</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>34</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>34</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>34</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>34</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>34</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>34</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>34</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>34</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>34</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>34</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>34</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>34</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>34</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>34</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>34</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>34</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>34</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>35</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>-192.73394900542564</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>35</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>-118.27008741302704</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>35</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>-296.3310550028155</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>35</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>-296.32321941843838</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>35</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>-620492.28245551535</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>35</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>-382994.76754579198</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>35</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>-951738.12149551569</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>35</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>-951738.12149551569</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>35</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>-0.13838189386612348</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>35</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>-8.5415310991562715E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>35</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>-0.21024240059966923</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>35</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>-0.21225618342252037</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>35</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>-5.4903145181676169E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>35</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>-3.388860413086032E-3</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>35</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>-8.3811362330694864E-3</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>35</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>-8.4212838317050658E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>35</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>632.79869730411281</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>35</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>487.2899516282277</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>35</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>117.74015608322394</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>35</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>117.74015608322394</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>39</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>-1977.716792433954</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>39</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>-6350000</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>39</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>-1.416173981362745</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>39</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>-5.6186834512101783E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>42</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>-1915.8359413274577</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>42</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>-6151314.6240000017</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>42</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>-1.3718632632574739</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>42</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>-5.4428802647332235E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>42</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>6560</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>45</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>-106933.15755961715</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>45</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>-29511.382259391237</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>45</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>-56045.031948099167</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>45</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>-33911.758173217677</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>45</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>315744918.53894621</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>45</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>191051105.68641928</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>45</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>165485939.54217994</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>45</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>100132321.59487532</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>45</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>-70.816317421555098</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>45</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>-43.007162555623744</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>45</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>-37.115735314605786</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>45</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>-22.458009151920123</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>45</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>-2.8024870185259525</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>45</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>-1.6991562110569889</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>45</v>
       </c>
@@ -6522,7 +6522,7 @@
         <v>-1.4688191957658538</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>45</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>-0.88875391155310213</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>45</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>-865054.57133957872</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>45</v>
       </c>
@@ -6591,7 +6591,7 @@
         <v>-523427.68681210757</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>45</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>-453386.13573199982</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>45</v>
       </c>
@@ -6637,15 +6637,15 @@
         <v>-274335.12765719264</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B261">
         <v>10</v>
       </c>
       <c r="F261" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G261" t="s">
         <v>31</v>
@@ -6657,15 +6657,15 @@
         <v>-970.5210144974626</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B262">
         <v>10</v>
       </c>
       <c r="F262" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G262" t="s">
         <v>31</v>
@@ -6674,18 +6674,18 @@
         <v>2</v>
       </c>
       <c r="K262" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.75">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B263">
         <v>10</v>
       </c>
       <c r="F263" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G263" t="s">
         <v>25</v>
@@ -6694,18 +6694,18 @@
         <v>2</v>
       </c>
       <c r="K263" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.75">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B264">
         <v>10</v>
       </c>
       <c r="F264" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G264" t="s">
         <v>25</v>
@@ -6717,15 +6717,15 @@
         <v>-1546.9363497933493</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B265">
         <v>10</v>
       </c>
       <c r="F265" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G265" t="s">
         <v>25</v>
@@ -6737,15 +6737,15 @@
         <v>-75.568855683948925</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B266">
         <v>10</v>
       </c>
       <c r="F266" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G266" t="s">
         <v>25</v>
@@ -6757,15 +6757,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B267">
         <v>10</v>
       </c>
       <c r="F267" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G267" t="s">
         <v>25</v>
@@ -6777,15 +6777,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B268">
         <v>10</v>
       </c>
       <c r="F268" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G268" t="s">
         <v>25</v>
@@ -6797,15 +6797,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B269">
         <v>10</v>
       </c>
       <c r="F269" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G269" t="s">
         <v>25</v>
@@ -6817,15 +6817,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B270">
         <v>10</v>
       </c>
       <c r="F270" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G270" t="s">
         <v>25</v>
@@ -6837,15 +6837,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B271">
         <v>10</v>
       </c>
       <c r="F271" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G271" t="s">
         <v>25</v>
@@ -6857,15 +6857,15 @@
         <v>-1.4839275036933885</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B272">
         <v>10</v>
       </c>
       <c r="F272" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G272" t="s">
         <v>25</v>
@@ -6874,18 +6874,18 @@
         <v>4</v>
       </c>
       <c r="K272" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.75">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B273">
         <v>10</v>
       </c>
       <c r="F273" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G273" t="s">
         <v>25</v>
@@ -6894,18 +6894,18 @@
         <v>4</v>
       </c>
       <c r="K273" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.75">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B274">
         <v>10</v>
       </c>
       <c r="F274" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G274" t="s">
         <v>25</v>
@@ -6917,15 +6917,15 @@
         <v>-10.088310085955754</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B275">
         <v>10</v>
       </c>
       <c r="F275" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G275" t="s">
         <v>25</v>
@@ -6937,15 +6937,15 @@
         <v>-6.6591967545296322</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B276">
         <v>10</v>
       </c>
       <c r="F276" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G276" t="s">
         <v>25</v>
@@ -6957,15 +6957,15 @@
         <v>-2.9877734973692387E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B277">
         <v>10</v>
       </c>
       <c r="F277" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G277" t="s">
         <v>25</v>
@@ -6974,18 +6974,18 @@
         <v>5</v>
       </c>
       <c r="K277" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.75">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B278">
         <v>10</v>
       </c>
       <c r="F278" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G278" t="s">
         <v>25</v>
@@ -6994,18 +6994,18 @@
         <v>5</v>
       </c>
       <c r="K278" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.75">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B279">
         <v>10</v>
       </c>
       <c r="F279" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G279" t="s">
         <v>25</v>
@@ -7017,15 +7017,15 @@
         <v>-0.21793961527363198</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B280">
         <v>10</v>
       </c>
       <c r="F280" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G280" t="s">
         <v>25</v>
@@ -7037,15 +7037,15 @@
         <v>-0.13276047223289916</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B281">
         <v>10</v>
       </c>
       <c r="F281" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G281" t="s">
         <v>25</v>
@@ -7057,15 +7057,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B282">
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G282" t="s">
         <v>25</v>
@@ -7077,15 +7077,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B283">
         <v>10</v>
       </c>
       <c r="F283" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G283" t="s">
         <v>25</v>
@@ -7097,15 +7097,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B284">
         <v>10</v>
       </c>
       <c r="F284" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G284" t="s">
         <v>25</v>
@@ -7117,15 +7117,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B285">
         <v>10</v>
       </c>
       <c r="F285" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G285" t="s">
         <v>25</v>
@@ -7137,15 +7137,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
+        <v>56</v>
+      </c>
+      <c r="B286">
+        <v>11</v>
+      </c>
+      <c r="D286" t="s">
         <v>57</v>
-      </c>
-      <c r="B286">
-        <v>11</v>
-      </c>
-      <c r="D286" t="s">
-        <v>58</v>
       </c>
       <c r="J286" t="s">
         <v>2</v>
@@ -7154,15 +7154,15 @@
         <v>-1808.8873101530066</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
+        <v>56</v>
+      </c>
+      <c r="B287">
+        <v>11</v>
+      </c>
+      <c r="D287" t="s">
         <v>57</v>
-      </c>
-      <c r="B287">
-        <v>11</v>
-      </c>
-      <c r="D287" t="s">
-        <v>58</v>
       </c>
       <c r="J287" t="s">
         <v>3</v>
@@ -7171,15 +7171,15 @@
         <v>-5807926.8292682925</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
+        <v>56</v>
+      </c>
+      <c r="B288">
+        <v>11</v>
+      </c>
+      <c r="D288" t="s">
         <v>57</v>
-      </c>
-      <c r="B288">
-        <v>11</v>
-      </c>
-      <c r="D288" t="s">
-        <v>58</v>
       </c>
       <c r="J288" t="s">
         <v>4</v>
@@ -7188,15 +7188,15 @@
         <v>-1.2952810805147057</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
+        <v>56</v>
+      </c>
+      <c r="B289">
+        <v>11</v>
+      </c>
+      <c r="D289" t="s">
         <v>57</v>
-      </c>
-      <c r="B289">
-        <v>11</v>
-      </c>
-      <c r="D289" t="s">
-        <v>58</v>
       </c>
       <c r="J289" t="s">
         <v>5</v>
@@ -7205,15 +7205,15 @@
         <v>-5.1390397419605292E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
+        <v>56</v>
+      </c>
+      <c r="B290">
+        <v>11</v>
+      </c>
+      <c r="D290" t="s">
         <v>57</v>
-      </c>
-      <c r="B290">
-        <v>11</v>
-      </c>
-      <c r="D290" t="s">
-        <v>58</v>
       </c>
       <c r="J290" t="s">
         <v>6</v>
@@ -7222,15 +7222,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B291">
         <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J291" t="s">
         <v>2</v>
@@ -7239,15 +7239,15 @@
         <v>-4876.9219885454231</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B292">
         <v>12</v>
       </c>
       <c r="E292" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J292" t="s">
         <v>2</v>
@@ -7256,15 +7256,15 @@
         <v>-1774.0668084404372</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B293">
         <v>12</v>
       </c>
       <c r="E293" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J293" t="s">
         <v>2</v>
@@ -7273,15 +7273,15 @@
         <v>-950.7241060990475</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B294">
         <v>12</v>
       </c>
       <c r="E294" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J294" t="s">
         <v>2</v>
@@ -7290,15 +7290,15 @@
         <v>-3020.0211762316617</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B295">
         <v>12</v>
       </c>
       <c r="E295" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J295" t="s">
         <v>2</v>
@@ -7307,15 +7307,15 @@
         <v>-933.59169847661292</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B296">
         <v>12</v>
       </c>
       <c r="E296" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J296" t="s">
         <v>3</v>
@@ -7324,15 +7324,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B297">
         <v>12</v>
       </c>
       <c r="E297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J297" t="s">
         <v>3</v>
@@ -7341,15 +7341,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B298">
         <v>12</v>
       </c>
       <c r="E298" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J298" t="s">
         <v>3</v>
@@ -7358,15 +7358,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B299">
         <v>12</v>
       </c>
       <c r="E299" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J299" t="s">
         <v>3</v>
@@ -7375,15 +7375,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B300">
         <v>12</v>
       </c>
       <c r="E300" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J300" t="s">
         <v>3</v>
@@ -7392,15 +7392,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B301">
         <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J301" t="s">
         <v>4</v>
@@ -7409,15 +7409,15 @@
         <v>-6.5137304738942357</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B302">
         <v>12</v>
       </c>
       <c r="E302" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J302" t="s">
         <v>4</v>
@@ -7426,15 +7426,15 @@
         <v>-2.3694849046189814</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B303">
         <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J303" t="s">
         <v>4</v>
@@ -7443,15 +7443,15 @@
         <v>-1.2698092355605342</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B304">
         <v>12</v>
       </c>
       <c r="E304" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J304" t="s">
         <v>4</v>
@@ -7460,15 +7460,15 @@
         <v>-21.407579723539779</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B305">
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J305" t="s">
         <v>4</v>
@@ -7477,15 +7477,15 @@
         <v>-6.6178140973538353</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B306">
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J306" t="s">
         <v>5</v>
@@ -7494,15 +7494,15 @@
         <v>-0.14160487679857303</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B307">
         <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J307" t="s">
         <v>5</v>
@@ -7511,15 +7511,15 @@
         <v>-5.1511283639903573E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B308">
         <v>12</v>
       </c>
       <c r="E308" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J308" t="s">
         <v>5</v>
@@ -7528,15 +7528,15 @@
         <v>-2.7604946363667927E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B309">
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J309" t="s">
         <v>5</v>
@@ -7545,15 +7545,15 @@
         <v>-0.4818824579629139</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B310">
         <v>12</v>
       </c>
       <c r="E310" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J310" t="s">
         <v>5</v>
@@ -7562,15 +7562,15 @@
         <v>-0.14896632710272495</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B311">
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J311" t="s">
         <v>6</v>
@@ -7579,15 +7579,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B312">
         <v>12</v>
       </c>
       <c r="E312" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J312" t="s">
         <v>6</v>
@@ -7596,15 +7596,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B313">
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J313" t="s">
         <v>6</v>
@@ -7613,15 +7613,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B314">
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J314" t="s">
         <v>6</v>
@@ -7630,15 +7630,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B315">
         <v>12</v>
       </c>
       <c r="E315" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J315" t="s">
         <v>6</v>
@@ -7647,18 +7647,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B316">
         <v>13</v>
       </c>
       <c r="D316" t="s">
+        <v>65</v>
+      </c>
+      <c r="H316" t="s">
         <v>66</v>
-      </c>
-      <c r="H316" t="s">
-        <v>67</v>
       </c>
       <c r="I316" t="s">
         <v>9</v>
@@ -7670,18 +7670,18 @@
         <v>3566.3983047165029</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B317">
         <v>13</v>
       </c>
       <c r="D317" t="s">
+        <v>65</v>
+      </c>
+      <c r="H317" t="s">
         <v>66</v>
-      </c>
-      <c r="H317" t="s">
-        <v>67</v>
       </c>
       <c r="I317" t="s">
         <v>11</v>
@@ -7693,15 +7693,15 @@
         <v>2168.1052472696442</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B318">
         <v>13</v>
       </c>
       <c r="D318" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H318" t="s">
         <v>50</v>
@@ -7716,15 +7716,15 @@
         <v>954.4859181741441</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B319">
         <v>13</v>
       </c>
       <c r="D319" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H319" t="s">
         <v>50</v>
@@ -7739,15 +7739,15 @@
         <v>796.8142232743877</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B320">
         <v>13</v>
       </c>
       <c r="D320" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H320" t="s">
         <v>50</v>
@@ -7762,15 +7762,15 @@
         <v>11450895.963258136</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B321">
         <v>13</v>
       </c>
       <c r="D321" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H321" t="s">
         <v>50</v>
@@ -7785,15 +7785,15 @@
         <v>6961294.14121967</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B322">
         <v>13</v>
       </c>
       <c r="D322" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H322" t="s">
         <v>50</v>
@@ -7808,15 +7808,15 @@
         <v>2809649.5744944243</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B323">
         <v>13</v>
       </c>
       <c r="D323" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H323" t="s">
         <v>50</v>
@@ -7831,15 +7831,15 @@
         <v>2345523.072416381</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B324">
         <v>13</v>
       </c>
       <c r="D324" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H324" t="s">
         <v>50</v>
@@ -7854,15 +7854,15 @@
         <v>2.6873437477385038</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B325">
         <v>13</v>
       </c>
       <c r="D325" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H325" t="s">
         <v>50</v>
@@ -7877,15 +7877,15 @@
         <v>1.6337053752475559</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B326">
         <v>13</v>
       </c>
       <c r="D326" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H326" t="s">
         <v>50</v>
@@ -7900,15 +7900,15 @@
         <v>0.65938021283055892</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B327">
         <v>13</v>
       </c>
       <c r="D327" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H327" t="s">
         <v>50</v>
@@ -7923,15 +7923,15 @@
         <v>0.55045708074367161</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B328">
         <v>13</v>
       </c>
       <c r="D328" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H328" t="s">
         <v>50</v>
@@ -7946,15 +7946,15 @@
         <v>0.10422494191183779</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B329">
         <v>13</v>
       </c>
       <c r="D329" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H329" t="s">
         <v>50</v>
@@ -7969,15 +7969,15 @@
         <v>6.3361022563460434E-2</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B330">
         <v>13</v>
       </c>
       <c r="D330" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H330" t="s">
         <v>50</v>
@@ -7992,15 +7992,15 @@
         <v>2.5573157299997012E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B331">
         <v>13</v>
       </c>
       <c r="D331" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H331" t="s">
         <v>50</v>
@@ -8015,15 +8015,15 @@
         <v>2.1348722995987782E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B332">
         <v>13</v>
       </c>
       <c r="D332" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H332" t="s">
         <v>50</v>
@@ -8038,15 +8038,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B333">
         <v>13</v>
       </c>
       <c r="D333" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H333" t="s">
         <v>50</v>
@@ -8061,15 +8061,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B334">
         <v>13</v>
       </c>
       <c r="D334" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H334" t="s">
         <v>50</v>
@@ -8084,15 +8084,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B335">
         <v>13</v>
       </c>
       <c r="D335" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H335" t="s">
         <v>50</v>
@@ -8107,15 +8107,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B336">
         <v>14</v>
       </c>
       <c r="D336" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J336" t="s">
         <v>2</v>
@@ -8124,15 +8124,15 @@
         <v>-1498.7846351502469</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B337">
         <v>14</v>
       </c>
       <c r="D337" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J337" t="s">
         <v>3</v>
@@ -8141,15 +8141,15 @@
         <v>-2163090.128755365</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B338">
         <v>14</v>
       </c>
       <c r="D338" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J338" t="s">
         <v>4</v>
@@ -8158,15 +8158,15 @@
         <v>-5.9438506206467459</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B339">
         <v>14</v>
       </c>
       <c r="D339" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J339" t="s">
         <v>5</v>
@@ -8175,15 +8175,15 @@
         <v>-0.15897340161396653</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B340">
         <v>14</v>
       </c>
       <c r="D340" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J340" t="s">
         <v>6</v>
